--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-location.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Location</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Location|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -355,7 +355,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,7 +520,7 @@
     <t>通常ベッド/部屋が位置する場所の稼働状況</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0116</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0116|2.0.0</t>
   </si>
   <si>
     <t>n/a</t>
@@ -622,7 +622,7 @@
     <t>場所で行われる機能のタイプを示します。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType|3.0.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -687,7 +687,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -790,7 +790,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -812,7 +812,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -916,7 +916,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1243,7 +1243,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="56.37890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.3671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1258,7 +1258,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="37.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-location.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Location|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Location</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -355,7 +355,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,7 +520,7 @@
     <t>通常ベッド/部屋が位置する場所の稼働状況</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0116|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0116</t>
   </si>
   <si>
     <t>n/a</t>
@@ -622,7 +622,7 @@
     <t>場所で行われる機能のタイプを示します。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
   </si>
   <si>
     <t>.code</t>
@@ -687,7 +687,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -790,7 +790,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
 </t>
   </si>
   <si>
@@ -812,7 +812,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -916,7 +916,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -1243,7 +1243,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.3671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1258,7 +1258,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="37.6796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
